--- a/vse-loti/341386519/spec-341386519.xlsx
+++ b/vse-loti/341386519/spec-341386519.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -95,6 +95,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -463,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1340,7 +1343,7 @@
         <v>131250</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>157500</v>
+        <v>160125</v>
       </c>
     </row>
     <row r="31">
@@ -1375,7 +1378,7 @@
         <v>131250</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>157500</v>
+        <v>160125</v>
       </c>
     </row>
     <row r="32">
@@ -1410,7 +1413,7 @@
         <v>128666.67</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>154400</v>
+        <v>156973.34</v>
       </c>
     </row>
     <row r="33">
@@ -1445,7 +1448,7 @@
         <v>128666.67</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>154400</v>
+        <v>156973.34</v>
       </c>
     </row>
     <row r="34">
@@ -1480,7 +1483,7 @@
         <v>128666.67</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>154400</v>
+        <v>156973.34</v>
       </c>
     </row>
     <row r="35">
@@ -1515,7 +1518,7 @@
         <v>114500</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>137400</v>
+        <v>139690</v>
       </c>
     </row>
     <row r="36">
@@ -1550,7 +1553,7 @@
         <v>114500</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>137400</v>
+        <v>139690</v>
       </c>
     </row>
     <row r="37">
@@ -1585,7 +1588,7 @@
         <v>114500</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>137400</v>
+        <v>139690</v>
       </c>
     </row>
     <row r="38">
@@ -1620,7 +1623,7 @@
         <v>114500</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>137400</v>
+        <v>139690</v>
       </c>
     </row>
     <row r="39">
@@ -1655,7 +1658,7 @@
         <v>117333.33</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>140800</v>
+        <v>143146.66</v>
       </c>
     </row>
     <row r="40">
@@ -1690,7 +1693,7 @@
         <v>116000</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>139200</v>
+        <v>141520</v>
       </c>
     </row>
     <row r="41">
@@ -1725,7 +1728,7 @@
         <v>117333.33</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>140800</v>
+        <v>143146.66</v>
       </c>
     </row>
     <row r="42">
@@ -1760,7 +1763,7 @@
         <v>231366.67</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>277640</v>
+        <v>282267.34</v>
       </c>
     </row>
     <row r="43">
@@ -1795,7 +1798,7 @@
         <v>231366.67</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>277640</v>
+        <v>282267.34</v>
       </c>
     </row>
     <row r="44">
@@ -1830,7 +1833,7 @@
         <v>231366.67</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>277640</v>
+        <v>282267.34</v>
       </c>
     </row>
     <row r="45">
@@ -1865,7 +1868,7 @@
         <v>231366.67</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>277640</v>
+        <v>282267.34</v>
       </c>
     </row>
     <row r="46">
@@ -1900,7 +1903,7 @@
         <v>231366.67</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>277640</v>
+        <v>282267.34</v>
       </c>
     </row>
     <row r="47">
@@ -1935,7 +1938,7 @@
         <v>231366.67</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>277640</v>
+        <v>282267.34</v>
       </c>
     </row>
     <row r="48">
@@ -1970,7 +1973,7 @@
         <v>231366.67</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>277640</v>
+        <v>282267.34</v>
       </c>
     </row>
     <row r="49">
@@ -2005,7 +2008,7 @@
         <v>231366.67</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>277640</v>
+        <v>282267.34</v>
       </c>
     </row>
     <row r="50">
@@ -2040,7 +2043,7 @@
         <v>231366.67</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>277640</v>
+        <v>282267.34</v>
       </c>
     </row>
     <row r="51">
@@ -2075,7 +2078,7 @@
         <v>231366.67</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>277640</v>
+        <v>282267.34</v>
       </c>
     </row>
     <row r="52">
@@ -2110,7 +2113,7 @@
         <v>231366.67</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>277640</v>
+        <v>282267.34</v>
       </c>
     </row>
     <row r="53">
@@ -2145,7 +2148,7 @@
         <v>231366.67</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>277640</v>
+        <v>282267.34</v>
       </c>
     </row>
     <row r="54">
@@ -2180,7 +2183,7 @@
         <v>162333.33</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>194800</v>
+        <v>198046.66</v>
       </c>
     </row>
     <row r="55">
@@ -2215,7 +2218,7 @@
         <v>185500</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>222600</v>
+        <v>226310</v>
       </c>
     </row>
     <row r="56">
@@ -2250,7 +2253,7 @@
         <v>187500</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>225000</v>
+        <v>228750</v>
       </c>
     </row>
     <row r="57">
@@ -2285,7 +2288,7 @@
         <v>190000</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>228000</v>
+        <v>231800</v>
       </c>
     </row>
     <row r="58">
@@ -3095,18 +3098,35 @@
         <v>4958900.04</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>НМЦК с НДС 22%:</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="n">
+        <v>6049858.05</v>
+      </c>
+    </row>
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
+          <t>НДС 22 %, ставка из документа: "евятьсот пятьдесят восемь тысяч девятьсот рублей 04 копейки) с учетом 22 % НДС." — IZVEShchENIE MUP UKKh truba.txt; закупка по 223-ФЗ, включать налоги в цену закон не требует — суммы взяты как в документе («без НДС»). «без НДС» — сумма из документа, «с НДС» = сумма × 1,22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
           <t>Источник: ИЗВЕЩЕНИЕ МУП УКХ труба.docx</t>
         </is>
       </c>
     </row>
-    <row r="90"/>
-    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A89:B91"/>
+    <mergeCell ref="A91:B93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/341386519/spec-341386519.xlsx
+++ b/vse-loti/341386519/spec-341386519.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -478,6 +478,7 @@
     <col width="20.28515625" customWidth="1" min="7" max="7"/>
     <col width="18.85546875" customWidth="1" min="8" max="8"/>
     <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="18.85546875" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -513,17 +514,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Цена за т (без НДС)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Стоимость (с НДС)</t>
         </is>
       </c>
     </row>
@@ -552,7 +558,7 @@
       <c r="F2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -580,7 +586,7 @@
       <c r="F3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -608,7 +614,7 @@
       <c r="F4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -636,7 +642,7 @@
       <c r="F5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -664,7 +670,7 @@
       <c r="F6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -692,7 +698,7 @@
       <c r="F7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -720,7 +726,7 @@
       <c r="F8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -748,7 +754,7 @@
       <c r="F9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -776,7 +782,7 @@
       <c r="F10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -804,7 +810,7 @@
       <c r="F11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -832,7 +838,7 @@
       <c r="F12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -860,7 +866,7 @@
       <c r="F13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -888,7 +894,7 @@
       <c r="F14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -916,7 +922,7 @@
       <c r="F15" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -944,7 +950,7 @@
       <c r="F16" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -972,7 +978,7 @@
       <c r="F17" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1000,7 +1006,7 @@
       <c r="F18" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1028,7 +1034,7 @@
       <c r="F19" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1056,7 +1062,7 @@
       <c r="F20" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1084,7 +1090,7 @@
       <c r="F21" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1112,7 +1118,7 @@
       <c r="F22" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1140,7 +1146,7 @@
       <c r="F23" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1168,7 +1174,7 @@
       <c r="F24" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1196,7 +1202,7 @@
       <c r="F25" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1224,7 +1230,7 @@
       <c r="F26" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1252,7 +1258,7 @@
       <c r="F27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1280,7 +1286,7 @@
       <c r="F28" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1308,7 +1314,7 @@
       <c r="F29" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1343,6 +1349,9 @@
         <v>131250</v>
       </c>
       <c r="I30" s="5" t="n">
+        <v>160125</v>
+      </c>
+      <c r="J30" s="5" t="n">
         <v>160125</v>
       </c>
     </row>
@@ -1380,6 +1389,9 @@
       <c r="I31" s="5" t="n">
         <v>160125</v>
       </c>
+      <c r="J31" s="5" t="n">
+        <v>160125</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1415,6 +1427,9 @@
       <c r="I32" s="5" t="n">
         <v>156973.34</v>
       </c>
+      <c r="J32" s="5" t="n">
+        <v>156973.34</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -1450,6 +1465,9 @@
       <c r="I33" s="5" t="n">
         <v>156973.34</v>
       </c>
+      <c r="J33" s="5" t="n">
+        <v>156973.34</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -1485,6 +1503,9 @@
       <c r="I34" s="5" t="n">
         <v>156973.34</v>
       </c>
+      <c r="J34" s="5" t="n">
+        <v>156973.34</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -1520,6 +1541,9 @@
       <c r="I35" s="5" t="n">
         <v>139690</v>
       </c>
+      <c r="J35" s="5" t="n">
+        <v>139690</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -1555,6 +1579,9 @@
       <c r="I36" s="5" t="n">
         <v>139690</v>
       </c>
+      <c r="J36" s="5" t="n">
+        <v>139690</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -1590,6 +1617,9 @@
       <c r="I37" s="5" t="n">
         <v>139690</v>
       </c>
+      <c r="J37" s="5" t="n">
+        <v>139690</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -1625,6 +1655,9 @@
       <c r="I38" s="5" t="n">
         <v>139690</v>
       </c>
+      <c r="J38" s="5" t="n">
+        <v>139690</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -1660,6 +1693,9 @@
       <c r="I39" s="5" t="n">
         <v>143146.66</v>
       </c>
+      <c r="J39" s="5" t="n">
+        <v>143146.66</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -1695,6 +1731,9 @@
       <c r="I40" s="5" t="n">
         <v>141520</v>
       </c>
+      <c r="J40" s="5" t="n">
+        <v>141520</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -1730,6 +1769,9 @@
       <c r="I41" s="5" t="n">
         <v>143146.66</v>
       </c>
+      <c r="J41" s="5" t="n">
+        <v>143146.66</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -1765,6 +1807,9 @@
       <c r="I42" s="5" t="n">
         <v>282267.34</v>
       </c>
+      <c r="J42" s="5" t="n">
+        <v>282267.34</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -1800,6 +1845,9 @@
       <c r="I43" s="5" t="n">
         <v>282267.34</v>
       </c>
+      <c r="J43" s="5" t="n">
+        <v>282267.34</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -1835,6 +1883,9 @@
       <c r="I44" s="5" t="n">
         <v>282267.34</v>
       </c>
+      <c r="J44" s="5" t="n">
+        <v>282267.34</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -1870,6 +1921,9 @@
       <c r="I45" s="5" t="n">
         <v>282267.34</v>
       </c>
+      <c r="J45" s="5" t="n">
+        <v>282267.34</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -1905,6 +1959,9 @@
       <c r="I46" s="5" t="n">
         <v>282267.34</v>
       </c>
+      <c r="J46" s="5" t="n">
+        <v>282267.34</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -1940,6 +1997,9 @@
       <c r="I47" s="5" t="n">
         <v>282267.34</v>
       </c>
+      <c r="J47" s="5" t="n">
+        <v>282267.34</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -1975,6 +2035,9 @@
       <c r="I48" s="5" t="n">
         <v>282267.34</v>
       </c>
+      <c r="J48" s="5" t="n">
+        <v>282267.34</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -2010,6 +2073,9 @@
       <c r="I49" s="5" t="n">
         <v>282267.34</v>
       </c>
+      <c r="J49" s="5" t="n">
+        <v>282267.34</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -2045,6 +2111,9 @@
       <c r="I50" s="5" t="n">
         <v>282267.34</v>
       </c>
+      <c r="J50" s="5" t="n">
+        <v>282267.34</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -2080,6 +2149,9 @@
       <c r="I51" s="5" t="n">
         <v>282267.34</v>
       </c>
+      <c r="J51" s="5" t="n">
+        <v>282267.34</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -2115,6 +2187,9 @@
       <c r="I52" s="5" t="n">
         <v>282267.34</v>
       </c>
+      <c r="J52" s="5" t="n">
+        <v>282267.34</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -2150,6 +2225,9 @@
       <c r="I53" s="5" t="n">
         <v>282267.34</v>
       </c>
+      <c r="J53" s="5" t="n">
+        <v>282267.34</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -2185,6 +2263,9 @@
       <c r="I54" s="5" t="n">
         <v>198046.66</v>
       </c>
+      <c r="J54" s="5" t="n">
+        <v>198046.66</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -2220,6 +2301,9 @@
       <c r="I55" s="5" t="n">
         <v>226310</v>
       </c>
+      <c r="J55" s="5" t="n">
+        <v>226310</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -2255,6 +2339,9 @@
       <c r="I56" s="5" t="n">
         <v>228750</v>
       </c>
+      <c r="J56" s="5" t="n">
+        <v>228750</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -2290,6 +2377,9 @@
       <c r="I57" s="5" t="n">
         <v>231800</v>
       </c>
+      <c r="J57" s="5" t="n">
+        <v>231800</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -2316,7 +2406,7 @@
       <c r="F58" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -2344,7 +2434,7 @@
       <c r="F59" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -2372,7 +2462,7 @@
       <c r="F60" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -2400,7 +2490,7 @@
       <c r="F61" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
@@ -2428,7 +2518,7 @@
       <c r="F62" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -2456,7 +2546,7 @@
       <c r="F63" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -2484,7 +2574,7 @@
       <c r="F64" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -2512,7 +2602,7 @@
       <c r="F65" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
@@ -2540,7 +2630,7 @@
       <c r="F66" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
@@ -2568,7 +2658,7 @@
       <c r="F67" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -2596,7 +2686,7 @@
       <c r="F68" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
@@ -2624,7 +2714,7 @@
       <c r="F69" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
@@ -2652,7 +2742,7 @@
       <c r="F70" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
@@ -2680,7 +2770,7 @@
       <c r="F71" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -2708,7 +2798,7 @@
       <c r="F72" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
@@ -2736,7 +2826,7 @@
       <c r="F73" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
@@ -2764,7 +2854,7 @@
       <c r="F74" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
@@ -2792,7 +2882,7 @@
       <c r="F75" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
@@ -2820,7 +2910,7 @@
       <c r="F76" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
@@ -2848,7 +2938,7 @@
       <c r="F77" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
@@ -2876,7 +2966,7 @@
       <c r="F78" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
@@ -2904,7 +2994,7 @@
       <c r="F79" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
@@ -2932,7 +3022,7 @@
       <c r="F80" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
@@ -2960,7 +3050,7 @@
       <c r="F81" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
@@ -2988,7 +3078,7 @@
       <c r="F82" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
@@ -3016,7 +3106,7 @@
       <c r="F83" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
@@ -3044,7 +3134,7 @@
       <c r="F84" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
@@ -3072,7 +3162,7 @@
       <c r="F85" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
@@ -3085,7 +3175,16 @@
         <v>84</v>
       </c>
       <c r="G86" s="8" t="n">
+        <v>59034.52</v>
+      </c>
+      <c r="H86" s="8" t="n">
         <v>4958900.04</v>
+      </c>
+      <c r="I86" s="8" t="n">
+        <v>72022.11</v>
+      </c>
+      <c r="J86" s="8" t="n">
+        <v>6049858.05</v>
       </c>
     </row>
     <row r="87">
@@ -3094,7 +3193,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G87" s="8" t="n">
+      <c r="H87" s="8" t="n">
         <v>4958900.04</v>
       </c>
     </row>
@@ -3104,7 +3203,7 @@
           <t>НМЦК с НДС 22%:</t>
         </is>
       </c>
-      <c r="F88" s="8" t="n">
+      <c r="J88" s="8" t="n">
         <v>6049858.05</v>
       </c>
     </row>
